--- a/memfail_experiment/experiment_results.xlsx
+++ b/memfail_experiment/experiment_results.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:Q109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3885,6 +3885,4074 @@
         <v>274</v>
       </c>
     </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>results_ablate_e0_baseline</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>coexisting_facts</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n"/>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="3" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>results_ablate_e0_baseline</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>conditional_easy</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="3" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>results_ablate_e0_baseline</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>conditional_hard</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="3" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>results_ablate_e0_baseline</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>long_hop</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>results_ablate_e0_baseline</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>persona_retrieval</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>0.9333</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="3" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>results_ablate_e0_baseline</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="L55" s="7" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="M55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>results_ablate_e1_m1</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>coexisting_facts</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="n"/>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L56" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q56" s="9" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>results_ablate_e1_m1</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>conditional_easy</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K57" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L57" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="9" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>results_ablate_e1_m1</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>conditional_hard</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L58" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="9" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>results_ablate_e1_m1</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>long_hop</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K59" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L59" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="9" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>results_ablate_e1_m1</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>persona_retrieval</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="n"/>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="L60" s="10" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="M60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q60" s="9" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>results_ablate_e1_m1</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="K61" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="L61" s="7" t="n">
+        <v>0.8286</v>
+      </c>
+      <c r="M61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>results_ablate_e2_m1_m3</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>coexisting_facts</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>results_ablate_e2_m1_m3</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>conditional_easy</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n"/>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="3" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>results_ablate_e2_m1_m3</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>conditional_hard</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L64" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q64" s="3" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>results_ablate_e2_m1_m3</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>long_hop</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>results_ablate_e2_m1_m3</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>persona_retrieval</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L66" s="4" t="n">
+        <v>0.9333</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="3" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>results_ablate_e2_m1_m3</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="K67" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="L67" s="7" t="n">
+        <v>0.7429</v>
+      </c>
+      <c r="M67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q67" s="6" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>results_ablate_e3_m1_m4</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>coexisting_facts</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="n"/>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q68" s="9" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>results_ablate_e3_m1_m4</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>conditional_easy</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="n"/>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L69" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="9" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>results_ablate_e3_m1_m4</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>conditional_hard</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="n"/>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q70" s="9" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>results_ablate_e3_m1_m4</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>long_hop</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="n"/>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K71" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L71" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="9" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>results_ablate_e3_m1_m4</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>persona_retrieval</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="n"/>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="L72" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="9" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>results_ablate_e3_m1_m4</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="n"/>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="K73" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="L73" s="7" t="n">
+        <v>0.6571</v>
+      </c>
+      <c r="M73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q73" s="6" t="n">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>results_ablate_e4_full</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>coexisting_facts</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q74" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>results_ablate_e4_full</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>conditional_easy</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L75" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" s="3" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>results_ablate_e4_full</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>conditional_hard</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q76" s="3" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>results_ablate_e4_full</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>long_hop</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L77" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>results_ablate_e4_full</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>persona_retrieval</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>0.9333</v>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" s="3" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>results_ablate_e4_full</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="n"/>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="K79" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="L79" s="7" t="n">
+        <v>0.7429</v>
+      </c>
+      <c r="M79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q79" s="6" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>results_cost_amem</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>coexisting_facts</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>amem</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="n"/>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L80" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" s="9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>results_cost_amem</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>conditional_easy</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>amem</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="n"/>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L81" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q81" s="9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>results_cost_amem</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>conditional_hard</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>amem</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="n"/>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L82" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" s="9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>results_cost_amem</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>long_hop</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>amem</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="n"/>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K83" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L83" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>results_cost_amem</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>persona_retrieval</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>amem</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="n"/>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="L84" s="10" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="M84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q84" s="9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>results_cost_amem</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>amem</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="n"/>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="L85" s="7" t="n">
+        <v>0.7714</v>
+      </c>
+      <c r="M85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P85" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q85" s="6" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>results_cost_letta</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>coexisting_facts</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>letta</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n"/>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>letta/letta-free</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q86" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>results_cost_letta</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>conditional_easy</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>letta</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>letta/letta-free</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>results_cost_letta</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>conditional_hard</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>letta</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>letta/letta-free</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>results_cost_letta</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>long_hop</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>letta</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n"/>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>letta/letta-free</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L89" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>results_cost_letta</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>persona_retrieval</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>letta</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n"/>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>letta/letta-free</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="L90" s="4" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="M90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q90" s="3" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>results_cost_letta</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>letta</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="n"/>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>letta/letta-free</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="K91" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="L91" s="7" t="n">
+        <v>0.5143</v>
+      </c>
+      <c r="M91" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="N91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q91" s="6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>results_cost_mem0v1</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>coexisting_facts</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>mem0</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>1.0.11</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>bge-m3:latest</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L92" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P92" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q92" s="9" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>results_cost_mem0v1</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>conditional_easy</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>mem0</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>1.0.11</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>bge-m3:latest</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L93" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q93" s="9" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>results_cost_mem0v1</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>conditional_hard</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>mem0</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>1.0.11</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>bge-m3:latest</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L94" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="9" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>results_cost_mem0v1</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>long_hop</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>mem0</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>1.0.11</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>bge-m3:latest</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L95" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>results_cost_mem0v1</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>persona_retrieval</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>mem0</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>1.0.11</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>bge-m3:latest</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="L96" s="10" t="n">
+        <v>0.9333</v>
+      </c>
+      <c r="M96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q96" s="9" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>results_cost_mem0v1</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>mem0</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>1.0.11</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>bge-m3:latest</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="K97" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="L97" s="7" t="n">
+        <v>0.7429</v>
+      </c>
+      <c r="M97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O97" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P97" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q97" s="6" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>results_cost_mem0v2</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>coexisting_facts</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>mem0</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>2.0.17</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>bge-m3:latest</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K98" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L98" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q98" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>results_cost_mem0v2</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>conditional_easy</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>mem0</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>2.0.17</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>bge-m3:latest</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K99" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L99" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q99" s="3" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>results_cost_mem0v2</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>conditional_hard</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>mem0</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>2.0.17</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>bge-m3:latest</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L100" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>results_cost_mem0v2</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>long_hop</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>mem0</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>2.0.17</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>bge-m3:latest</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L101" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>results_cost_mem0v2</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>persona_retrieval</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>mem0</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>2.0.17</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>bge-m3:latest</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K102" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="L102" s="4" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="M102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q102" s="3" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>results_cost_mem0v2</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>mem0</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>2.0.17</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>bge-m3:latest</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="K103" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="L103" s="7" t="n">
+        <v>0.7714</v>
+      </c>
+      <c r="M103" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N103" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O103" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P103" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q103" s="6" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="104" ht="16" customHeight="1">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>results_cost_structmem</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>coexisting_facts</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="n"/>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="9" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>results_cost_structmem</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>conditional_easy</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="n"/>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L105" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="9" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>results_cost_structmem</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>conditional_hard</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="n"/>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L106" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q106" s="9" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="107" ht="16" customHeight="1">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>results_cost_structmem</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>long_hop</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="n"/>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L107" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="9" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>results_cost_structmem</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>persona_retrieval</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="n"/>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="L108" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q108" s="9" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="109" ht="16" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>results_cost_structmem</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>structmem</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="n"/>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>sentence-transformers/all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="K109" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="L109" s="7" t="n">
+        <v>0.6571</v>
+      </c>
+      <c r="M109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="P109" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q109" s="6" t="n">
+        <v>274</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
